--- a/SuppXLS/Scen_UC_BIO_CEMENTHEAT_15_30.xlsx
+++ b/SuppXLS/Scen_UC_BIO_CEMENTHEAT_15_30.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62FD6BE8-E4B8-460B-9DB5-5F688435F6D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F98B920-39FA-438A-B93F-8AE5FB561392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
   </bookViews>
   <sheets>
     <sheet name="BIO_CEMENTHEAT_15_30" sheetId="1" r:id="rId1"/>
@@ -629,7 +629,7 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <v>-0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -668,7 +668,7 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>-0.3</v>
+        <v>-0.35</v>
       </c>
       <c r="M7">
         <v>0</v>

--- a/SuppXLS/Scen_UC_BIO_CEMENTHEAT_15_30.xlsx
+++ b/SuppXLS/Scen_UC_BIO_CEMENTHEAT_15_30.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F98B920-39FA-438A-B93F-8AE5FB561392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D61BC665-5645-4AD4-A530-1E5069A47A5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
   </bookViews>
   <sheets>
-    <sheet name="BIO_CEMENTHEAT_15_30" sheetId="1" r:id="rId1"/>
+    <sheet name="BIO_CEMENTHEAT_10_20" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -110,7 +110,7 @@
     <t>Minimum Bioenergy  penetration for cement process heat</t>
   </si>
   <si>
-    <t>UC_BIO_CEMENTHEAT_15_30</t>
+    <t>UC_BIO_CEMENTHEAT_10_20</t>
   </si>
 </sst>
 </file>
@@ -668,7 +668,7 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>-0.35</v>
+        <v>-0.2</v>
       </c>
       <c r="M7">
         <v>0</v>

--- a/SuppXLS/Scen_UC_BIO_CEMENTHEAT_15_30.xlsx
+++ b/SuppXLS/Scen_UC_BIO_CEMENTHEAT_15_30.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D61BC665-5645-4AD4-A530-1E5069A47A5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85A83D84-8CAA-4502-8A1D-B04E718158B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{58752476-08F6-480F-B14A-373304AB5756}"/>
   </bookViews>
   <sheets>
-    <sheet name="BIO_CEMENTHEAT_10_20" sheetId="1" r:id="rId1"/>
+    <sheet name="BIO_CEMENTHEAT_15_30" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -110,7 +110,7 @@
     <t>Minimum Bioenergy  penetration for cement process heat</t>
   </si>
   <si>
-    <t>UC_BIO_CEMENTHEAT_10_20</t>
+    <t>UC_BIO_CEMENTHEAT_15_30</t>
   </si>
 </sst>
 </file>
@@ -629,7 +629,7 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <v>-0.1</v>
+        <v>-0.15</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -668,7 +668,7 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="M7">
         <v>0</v>
